--- a/Result/profitability/6192.xlsx
+++ b/Result/profitability/6192.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.77</v>
       </c>
       <c r="M2" t="n">
-        <v>2.3625</v>
+        <v>2.43125</v>
       </c>
       <c r="N2" t="n">
-        <v>30.8575</v>
+        <v>31.735</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.22</v>
       </c>
       <c r="M3" t="n">
-        <v>2.25</v>
+        <v>2.16875</v>
       </c>
       <c r="N3" t="n">
-        <v>30.46875</v>
+        <v>30.76875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.94</v>
       </c>
       <c r="M4" t="n">
-        <v>2.0775</v>
+        <v>2.04625</v>
       </c>
       <c r="N4" t="n">
-        <v>29.7125</v>
+        <v>29.8525</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.72</v>
       </c>
       <c r="M5" t="n">
-        <v>1.9275</v>
+        <v>1.9975</v>
       </c>
       <c r="N5" t="n">
-        <v>28.91</v>
+        <v>28.54875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.11</v>
       </c>
       <c r="M6" t="n">
-        <v>1.8025</v>
+        <v>1.80625</v>
       </c>
       <c r="N6" t="n">
-        <v>27.23875</v>
+        <v>27.305</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.4</v>
       </c>
       <c r="M7" t="n">
-        <v>1.6475</v>
+        <v>1.6825</v>
       </c>
       <c r="N7" t="n">
-        <v>25.97125</v>
+        <v>26.285</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.55</v>
       </c>
       <c r="M8" t="n">
-        <v>1.5425</v>
+        <v>1.5475</v>
       </c>
       <c r="N8" t="n">
-        <v>24.97125</v>
+        <v>24.865</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6192</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2053</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1372</v>
+      </c>
+      <c r="E75" t="n">
+        <v>681</v>
+      </c>
+      <c r="F75" t="n">
+        <v>33.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>351</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>17.08%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>17</v>
+      </c>
+      <c r="J75" t="n">
+        <v>367</v>
+      </c>
+      <c r="K75" t="n">
+        <v>257</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.94</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.04000000000000004</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.01520912547528508</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.8500000000000014</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02498530276308053</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.2654028436018958</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.890000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.0801442041042707</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
